--- a/public/assets/data/exercises.xlsx
+++ b/public/assets/data/exercises.xlsx
@@ -1,56 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\CodeDthu-updated\assets\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C60810-C175-4E5D-B7E9-1AB56383A098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Subjects" sheetId="1" r:id="rId1"/>
     <sheet name="Exercises" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>CS Exercise Hub</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>Cột 'id' phải là duy nhất, dùng để liên kết với subjectId ở sheet Exercises.</t>
+          <t xml:space="preserve">Cột 'id' phải là duy nhất, dùng để liên kết với subjectId ở sheet Exercises.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>Nhiều chủ đề cách nhau bởi dấu | (ví dụ: Mảng|Con trỏ|Vòng lặp)</t>
+          <t xml:space="preserve">Nhiều chủ đề cách nhau bởi dấu | (ví dụ: Mảng|Con trỏ|Vòng lặp)</t>
         </r>
       </text>
     </comment>
@@ -59,78 +49,68 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>CS Exercise Hub</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>id duy nhất, quy ước: &lt;subjectId&gt;-&lt;số&gt;, ví dụ python-8</t>
+          <t xml:space="preserve">id duy nhất, quy ước: &lt;subjectId&gt;-&lt;số&gt;, ví dụ python-8</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>Phải trùng với 1 giá trị 'id' ở sheet Subjects.</t>
+          <t xml:space="preserve">Phải trùng với 1 giá trị 'id' ở sheet Subjects.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>Định dạng YYYY-MM-DD. Đã đặt cố định 2026-08-10 theo yêu cầu, có thể tự sửa lại.</t>
+          <t xml:space="preserve">Định dạng YYYY-MM-DD. Đã đặt cố định 2026-08-10 theo yêu cầu, có thể tự sửa lại.</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>Ô tô vàng: để trống, người dùng tự điền mô tả dữ liệu đầu vào.</t>
+          <t xml:space="preserve">Ô tô vàng: để trống, người dùng tự điền mô tả dữ liệu đầu vào.</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>Ô tô vàng: để trống, người dùng tự điền mô tả dữ liệu đầu ra.</t>
+          <t xml:space="preserve">Ô tô vàng: để trống, người dùng tự điền mô tả dữ liệu đầu ra.</t>
         </r>
       </text>
     </comment>
@@ -139,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="286" count="286">
   <si>
     <t>id</t>
   </si>
@@ -994,29 +974,32 @@
   </si>
   <si>
     <t>100 131</t>
+  </si>
+  <si>
+    <t>Bài tập tính tổng</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="0" formatCode="General"/>
+  </numFmts>
+  <fonts count="3">
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="10"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1049,11 +1032,15 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1064,18 +1051,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
 </styleSheet>
 </file>
 
@@ -1296,7 +1275,7 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
+            <a:lightRig dir="t" rig="threePt">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
@@ -1363,19 +1342,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="12.0" style="0"/>
+    <col min="2" max="2" customWidth="1" width="26.0" style="0"/>
+    <col min="3" max="3" customWidth="1" width="46.0" style="0"/>
+    <col min="4" max="4" customWidth="1" width="12.0" style="0"/>
+    <col min="5" max="5" customWidth="1" width="22.0" style="0"/>
+    <col min="6" max="6" customWidth="1" width="46.0" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="8:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1395,7 +1374,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="8:8" ht="25.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -1415,7 +1394,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="8:8" ht="25.5" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>55</v>
       </c>
@@ -1435,7 +1414,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="8:8" ht="25.5" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>92</v>
       </c>
@@ -1455,7 +1434,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="8:8" ht="25.5" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>122</v>
       </c>
@@ -1475,7 +1454,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="8:8" ht="25.5" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>153</v>
       </c>
@@ -1495,7 +1474,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="8:8" ht="25.5" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>190</v>
       </c>
@@ -1515,7 +1494,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="8:8" ht="25.5" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>223</v>
       </c>
@@ -1536,28 +1515,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:O50"/>
+  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="46" customWidth="1"/>
-    <col min="10" max="12" width="30" customWidth="1"/>
+    <col min="1" max="2" customWidth="1" width="12.0" style="0"/>
+    <col min="3" max="3" customWidth="1" width="26.0" style="0"/>
+    <col min="4" max="4" customWidth="1" width="40.0" style="0"/>
+    <col min="5" max="5" customWidth="1" width="12.0" style="0"/>
+    <col min="6" max="6" customWidth="1" width="14.0" style="0"/>
+    <col min="7" max="7" customWidth="1" width="12.0" style="0"/>
+    <col min="8" max="8" customWidth="1" width="14.0" style="0"/>
+    <col min="9" max="9" customWidth="1" width="46.0" style="0"/>
+    <col min="10" max="12" customWidth="1" width="30.0" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="8:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1601,7 +1580,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="8:8" ht="89.25" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1609,11 +1588,9 @@
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
         <v>18</v>
       </c>
@@ -1634,16 +1611,16 @@
         <v>283</v>
       </c>
       <c r="L2" s="3">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="M2" t="s">
         <v>284</v>
       </c>
       <c r="N2">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+        <v>231.0</v>
+      </c>
+    </row>
+    <row r="3" spans="8:8" ht="102.0" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -1675,7 +1652,7 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:14" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="8:8" ht="102.0" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -1707,7 +1684,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="8:8" ht="89.25" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1739,7 +1716,7 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="8:8" ht="89.25" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
@@ -1771,7 +1748,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="8:8" ht="89.25" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>44</v>
       </c>
@@ -1803,7 +1780,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="8:8" ht="102.0" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -1835,7 +1812,7 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="8:8" ht="89.25" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
@@ -1867,7 +1844,7 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="8:8" ht="89.25" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
@@ -1899,7 +1876,7 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="8:8" ht="89.25" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -1931,7 +1908,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="8:8" ht="89.25" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>71</v>
       </c>
@@ -1963,7 +1940,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="8:8" ht="89.25" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>76</v>
       </c>
@@ -1995,7 +1972,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="8:8" ht="89.25" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>81</v>
       </c>
@@ -2027,7 +2004,7 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="8:8" ht="89.25" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>86</v>
       </c>
@@ -2059,7 +2036,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="8:8" ht="89.25" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>91</v>
       </c>
@@ -2091,7 +2068,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:8" ht="89.25" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>97</v>
       </c>
@@ -2123,7 +2100,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="8:8" ht="89.25" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>101</v>
       </c>
@@ -2155,7 +2132,7 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="8:8" ht="89.25" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>105</v>
       </c>
@@ -2187,7 +2164,7 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="8:8" ht="89.25" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>109</v>
       </c>
@@ -2219,7 +2196,7 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="8:8" ht="89.25" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>113</v>
       </c>
@@ -2251,7 +2228,7 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="8:8" ht="89.25" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>117</v>
       </c>
@@ -2283,7 +2260,7 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="8:8" ht="89.25" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>121</v>
       </c>
@@ -2315,7 +2292,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="8:8" ht="89.25" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>127</v>
       </c>
@@ -2347,7 +2324,7 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="8:8" ht="89.25" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>131</v>
       </c>
@@ -2379,7 +2356,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="8:8" ht="89.25" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>135</v>
       </c>
@@ -2411,7 +2388,7 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
     </row>
-    <row r="27" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="8:8" ht="89.25" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>139</v>
       </c>
@@ -2443,7 +2420,7 @@
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
-    <row r="28" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="8:8" ht="89.25" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>143</v>
       </c>
@@ -2475,7 +2452,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="8:8" ht="89.25" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>147</v>
       </c>
@@ -2507,7 +2484,7 @@
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="8:8" ht="102.0" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>152</v>
       </c>
@@ -2539,7 +2516,7 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="8:8" ht="102.0" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>159</v>
       </c>
@@ -2571,7 +2548,7 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="8:8" ht="102.0" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>164</v>
       </c>
@@ -2603,7 +2580,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="8:8" ht="102.0" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>169</v>
       </c>
@@ -2635,7 +2612,7 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="8:8" ht="102.0" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>174</v>
       </c>
@@ -2667,7 +2644,7 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="8:8" ht="102.0" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>179</v>
       </c>
@@ -2699,7 +2676,7 @@
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="8:8" ht="102.0" customHeight="1">
       <c r="A36" s="2" t="s">
         <v>184</v>
       </c>
@@ -2731,7 +2708,7 @@
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
     </row>
-    <row r="37" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="8:8" ht="102.0" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>189</v>
       </c>
@@ -2763,7 +2740,7 @@
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
     </row>
-    <row r="38" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="8:8" ht="102.0" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>194</v>
       </c>
@@ -2795,7 +2772,7 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="8:8" ht="102.0" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>198</v>
       </c>
@@ -2827,7 +2804,7 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
     </row>
-    <row r="40" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="8:8" ht="102.0" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>203</v>
       </c>
@@ -2859,7 +2836,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
     </row>
-    <row r="41" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="8:8" ht="102.0" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>208</v>
       </c>
@@ -2891,7 +2868,7 @@
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
     </row>
-    <row r="42" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="8:8" ht="102.0" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>212</v>
       </c>
@@ -2923,7 +2900,7 @@
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
     </row>
-    <row r="43" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="8:8" ht="102.0" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>217</v>
       </c>
@@ -2955,7 +2932,7 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="8:8" ht="102.0" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>222</v>
       </c>
@@ -2987,7 +2964,7 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="8:8" ht="102.0" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>227</v>
       </c>
@@ -3019,7 +2996,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="8:8" ht="102.0" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>231</v>
       </c>
@@ -3051,7 +3028,7 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="8:8" ht="102.0" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>235</v>
       </c>
@@ -3083,7 +3060,7 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="8:8" ht="102.0" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>239</v>
       </c>
@@ -3115,7 +3092,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="49" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="8:8" ht="102.0" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>244</v>
       </c>
@@ -3147,7 +3124,7 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="8:8" ht="102.0" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>249</v>
       </c>
@@ -3180,7 +3157,7 @@
       <c r="L50" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>